--- a/data/WAO_farms_data.xlsx
+++ b/data/WAO_farms_data.xlsx
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>1</v>

--- a/data/WAO_farms_data.xlsx
+++ b/data/WAO_farms_data.xlsx
@@ -360,8 +360,8 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Z10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="4" min="6" max="6"/>
   </cols>
@@ -421,21 +421,21 @@
     <row r="2" ht="15.75" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>VIChac</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
@@ -445,21 +445,21 @@
     <row r="3" ht="15.75" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>farm,hacen</t>
+          <t>hac</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ViC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
@@ -469,21 +469,21 @@
     <row r="4" ht="15.75" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>haac</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -493,14 +493,14 @@
     <row r="5" ht="15.75" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>kazuru_farm6</t>
+          <t>VIChac</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1</v>
@@ -511,47 +511,47 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>kazuru_farm5</t>
+          <t>farm,hacen</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>ViC</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>hac</t>
+          <t>kazuru_farm5</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -559,44 +559,66 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>haac</t>
+          <t>kazuru_farm6</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>zuchin</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="5">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>zahino</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/WAO_farms_data.xlsx
+++ b/data/WAO_farms_data.xlsx
@@ -617,6 +617,9 @@
       <c r="C10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
       </c>

--- a/data/WAO_farms_data.xlsx
+++ b/data/WAO_farms_data.xlsx
@@ -360,7 +360,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="4" min="6" max="6"/>
@@ -397,26 +397,6 @@
           <t>marches_limit</t>
         </is>
       </c>
-      <c r="G1" s="7" t="n"/>
-      <c r="H1" s="7" t="n"/>
-      <c r="I1" s="7" t="n"/>
-      <c r="J1" s="7" t="n"/>
-      <c r="K1" s="7" t="n"/>
-      <c r="L1" s="7" t="n"/>
-      <c r="M1" s="7" t="n"/>
-      <c r="N1" s="7" t="n"/>
-      <c r="O1" s="7" t="n"/>
-      <c r="P1" s="7" t="n"/>
-      <c r="Q1" s="7" t="n"/>
-      <c r="R1" s="7" t="n"/>
-      <c r="S1" s="7" t="n"/>
-      <c r="T1" s="7" t="n"/>
-      <c r="U1" s="7" t="n"/>
-      <c r="V1" s="7" t="n"/>
-      <c r="W1" s="7" t="n"/>
-      <c r="X1" s="7" t="n"/>
-      <c r="Y1" s="7" t="n"/>
-      <c r="Z1" s="7" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
@@ -612,10 +592,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>2</v>
